--- a/F746ZG Pinout.xlsx
+++ b/F746ZG Pinout.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phil\Documents\code\dmx_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5BBFEEFA-62BD-472C-91D4-89231AC41C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5743A525-04F7-454A-9CC7-52EB0866574F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{F8CA67F0-8857-44BA-BC1A-84BB4FF21958}"/>
+    <workbookView xWindow="8960" yWindow="2180" windowWidth="25630" windowHeight="19110" activeTab="1" xr2:uid="{F8CA67F0-8857-44BA-BC1A-84BB4FF21958}"/>
   </bookViews>
   <sheets>
     <sheet name="Full Pinout" sheetId="1" r:id="rId1"/>
@@ -5835,11 +5835,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5907FD9C-359D-49C9-8A94-20DB146B0C12}">
   <dimension ref="B1:D43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.08984375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
